--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$149</f>
+              <f>'Daily Performance'!$B$2:$B$150</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$149</f>
+              <f>'Daily Performance'!$G$2:$G$150</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$149</f>
+              <f>'Daily Performance'!$B$2:$B$150</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$149</f>
+              <f>'Daily Performance'!$I$2:$I$150</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M149"/>
+  <dimension ref="A1:M150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8862,6 +8862,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="150">
+      <c r="A150" s="27" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C150" s="28" t="n">
+        <v>68894.92999999999</v>
+      </c>
+      <c r="D150" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150" s="29" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F150" s="28" t="n">
+        <v>472544.59</v>
+      </c>
+      <c r="G150" s="28" t="n">
+        <v>472544.59</v>
+      </c>
+      <c r="H150" s="37" t="n">
+        <v>-27455.41</v>
+      </c>
+      <c r="I150" s="38" t="n">
+        <v>-0.0549</v>
+      </c>
+      <c r="J150" s="27" t="inlineStr">
+        <is>
+          <t>ซื้อ</t>
+        </is>
+      </c>
+      <c r="K150" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L150" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" s="27" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$150</f>
+              <f>'Daily Performance'!$B$2:$B$151</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$150</f>
+              <f>'Daily Performance'!$G$2:$G$151</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$150</f>
+              <f>'Daily Performance'!$B$2:$B$151</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$150</f>
+              <f>'Daily Performance'!$I$2:$I$151</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M150"/>
+  <dimension ref="A1:M151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8907,6 +8907,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="151">
+      <c r="A151" s="32" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="32" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C151" s="33" t="n">
+        <v>68430</v>
+      </c>
+      <c r="D151" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E151" s="34" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F151" s="33" t="n">
+        <v>469355.68</v>
+      </c>
+      <c r="G151" s="33" t="n">
+        <v>469355.68</v>
+      </c>
+      <c r="H151" s="39" t="n">
+        <v>-30644.32</v>
+      </c>
+      <c r="I151" s="40" t="n">
+        <v>-0.0613</v>
+      </c>
+      <c r="J151" s="32" t="inlineStr">
+        <is>
+          <t>ขาย</t>
+        </is>
+      </c>
+      <c r="K151" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" s="32" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$151</f>
+              <f>'Daily Performance'!$B$2:$B$152</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$151</f>
+              <f>'Daily Performance'!$G$2:$G$152</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$151</f>
+              <f>'Daily Performance'!$B$2:$B$152</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$151</f>
+              <f>'Daily Performance'!$I$2:$I$152</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M151"/>
+  <dimension ref="A1:M152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8952,6 +8952,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" s="27" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C152" s="28" t="n">
+        <v>68164.45</v>
+      </c>
+      <c r="D152" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" s="29" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F152" s="28" t="n">
+        <v>467534.28</v>
+      </c>
+      <c r="G152" s="28" t="n">
+        <v>467534.28</v>
+      </c>
+      <c r="H152" s="37" t="n">
+        <v>-32465.72</v>
+      </c>
+      <c r="I152" s="38" t="n">
+        <v>-0.0649</v>
+      </c>
+      <c r="J152" s="27" t="inlineStr">
+        <is>
+          <t>ถือ</t>
+        </is>
+      </c>
+      <c r="K152" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L152" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" s="27" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$152</f>
+              <f>'Daily Performance'!$B$2:$B$153</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$152</f>
+              <f>'Daily Performance'!$G$2:$G$153</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$152</f>
+              <f>'Daily Performance'!$B$2:$B$153</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$152</f>
+              <f>'Daily Performance'!$I$2:$I$153</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M152"/>
+  <dimension ref="A1:M153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8997,6 +8997,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="153">
+      <c r="A153" s="32" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="32" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C153" s="33" t="n">
+        <v>68664.03999999999</v>
+      </c>
+      <c r="D153" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" s="34" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F153" s="33" t="n">
+        <v>470960.93</v>
+      </c>
+      <c r="G153" s="33" t="n">
+        <v>470960.93</v>
+      </c>
+      <c r="H153" s="39" t="n">
+        <v>-29039.07</v>
+      </c>
+      <c r="I153" s="40" t="n">
+        <v>-0.0581</v>
+      </c>
+      <c r="J153" s="32" t="inlineStr">
+        <is>
+          <t>ซื้อ</t>
+        </is>
+      </c>
+      <c r="K153" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" s="32" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$153</f>
+              <f>'Daily Performance'!$B$2:$B$154</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$153</f>
+              <f>'Daily Performance'!$G$2:$G$154</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$153</f>
+              <f>'Daily Performance'!$B$2:$B$154</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$153</f>
+              <f>'Daily Performance'!$I$2:$I$154</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M153"/>
+  <dimension ref="A1:M154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9042,6 +9042,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="154">
+      <c r="A154" s="27" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C154" s="28" t="n">
+        <v>68471.73</v>
+      </c>
+      <c r="D154" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E154" s="29" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F154" s="28" t="n">
+        <v>469641.9</v>
+      </c>
+      <c r="G154" s="28" t="n">
+        <v>469641.9</v>
+      </c>
+      <c r="H154" s="37" t="n">
+        <v>-30358.1</v>
+      </c>
+      <c r="I154" s="38" t="n">
+        <v>-0.0607</v>
+      </c>
+      <c r="J154" s="27" t="inlineStr">
+        <is>
+          <t>ถือ</t>
+        </is>
+      </c>
+      <c r="K154" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L154" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" s="27" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$154</f>
+              <f>'Daily Performance'!$B$2:$B$155</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$154</f>
+              <f>'Daily Performance'!$G$2:$G$155</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$154</f>
+              <f>'Daily Performance'!$B$2:$B$155</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$154</f>
+              <f>'Daily Performance'!$I$2:$I$155</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M154"/>
+  <dimension ref="A1:M155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9087,6 +9087,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="155">
+      <c r="A155" s="32" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="32" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C155" s="33" t="n">
+        <v>69746.41</v>
+      </c>
+      <c r="D155" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155" s="34" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F155" s="33" t="n">
+        <v>478384.81</v>
+      </c>
+      <c r="G155" s="33" t="n">
+        <v>478384.81</v>
+      </c>
+      <c r="H155" s="39" t="n">
+        <v>-21615.19</v>
+      </c>
+      <c r="I155" s="40" t="n">
+        <v>-0.0432</v>
+      </c>
+      <c r="J155" s="32" t="inlineStr">
+        <is>
+          <t>ซื้อ</t>
+        </is>
+      </c>
+      <c r="K155" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L155" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" s="32" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$155</f>
+              <f>'Daily Performance'!$B$2:$B$156</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$155</f>
+              <f>'Daily Performance'!$G$2:$G$156</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$155</f>
+              <f>'Daily Performance'!$B$2:$B$156</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$155</f>
+              <f>'Daily Performance'!$I$2:$I$156</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M155"/>
+  <dimension ref="A1:M156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9132,6 +9132,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="156">
+      <c r="A156" s="27" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C156" s="28" t="n">
+        <v>69526.44</v>
+      </c>
+      <c r="D156" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E156" s="29" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F156" s="28" t="n">
+        <v>476876.07</v>
+      </c>
+      <c r="G156" s="28" t="n">
+        <v>476876.07</v>
+      </c>
+      <c r="H156" s="37" t="n">
+        <v>-23123.93</v>
+      </c>
+      <c r="I156" s="38" t="n">
+        <v>-0.0462</v>
+      </c>
+      <c r="J156" s="27" t="inlineStr">
+        <is>
+          <t>ถือ</t>
+        </is>
+      </c>
+      <c r="K156" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L156" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" s="27" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$156</f>
+              <f>'Daily Performance'!$B$2:$B$157</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$156</f>
+              <f>'Daily Performance'!$G$2:$G$157</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$156</f>
+              <f>'Daily Performance'!$B$2:$B$157</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$156</f>
+              <f>'Daily Performance'!$I$2:$I$157</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M156"/>
+  <dimension ref="A1:M157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9177,6 +9177,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="157">
+      <c r="A157" s="32" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="32" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C157" s="33" t="n">
+        <v>69668.14999999999</v>
+      </c>
+      <c r="D157" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E157" s="34" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F157" s="33" t="n">
+        <v>477847.99</v>
+      </c>
+      <c r="G157" s="33" t="n">
+        <v>477847.99</v>
+      </c>
+      <c r="H157" s="39" t="n">
+        <v>-22152.01</v>
+      </c>
+      <c r="I157" s="40" t="n">
+        <v>-0.0443</v>
+      </c>
+      <c r="J157" s="32" t="inlineStr">
+        <is>
+          <t>ถือ</t>
+        </is>
+      </c>
+      <c r="K157" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L157" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" s="32" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$157</f>
+              <f>'Daily Performance'!$B$2:$B$158</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$157</f>
+              <f>'Daily Performance'!$G$2:$G$158</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$157</f>
+              <f>'Daily Performance'!$B$2:$B$158</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$157</f>
+              <f>'Daily Performance'!$I$2:$I$158</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M157"/>
+  <dimension ref="A1:M158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9222,6 +9222,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="158">
+      <c r="A158" s="27" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C158" s="28" t="n">
+        <v>69137.56</v>
+      </c>
+      <c r="D158" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E158" s="29" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F158" s="28" t="n">
+        <v>474208.73</v>
+      </c>
+      <c r="G158" s="28" t="n">
+        <v>474208.73</v>
+      </c>
+      <c r="H158" s="37" t="n">
+        <v>-25791.27</v>
+      </c>
+      <c r="I158" s="38" t="n">
+        <v>-0.0516</v>
+      </c>
+      <c r="J158" s="27" t="inlineStr">
+        <is>
+          <t>ขาย</t>
+        </is>
+      </c>
+      <c r="K158" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" s="27" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$158</f>
+              <f>'Daily Performance'!$B$2:$B$159</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$158</f>
+              <f>'Daily Performance'!$G$2:$G$159</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$158</f>
+              <f>'Daily Performance'!$B$2:$B$159</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$158</f>
+              <f>'Daily Performance'!$I$2:$I$159</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M158"/>
+  <dimension ref="A1:M159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9267,6 +9267,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="159">
+      <c r="A159" s="32" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="32" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C159" s="33" t="n">
+        <v>68420.60000000001</v>
+      </c>
+      <c r="D159" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E159" s="34" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F159" s="33" t="n">
+        <v>469291.19</v>
+      </c>
+      <c r="G159" s="33" t="n">
+        <v>469291.19</v>
+      </c>
+      <c r="H159" s="39" t="n">
+        <v>-30708.81</v>
+      </c>
+      <c r="I159" s="40" t="n">
+        <v>-0.0614</v>
+      </c>
+      <c r="J159" s="32" t="inlineStr">
+        <is>
+          <t>ขาย</t>
+        </is>
+      </c>
+      <c r="K159" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" s="32" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$159</f>
+              <f>'Daily Performance'!$B$2:$B$160</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$159</f>
+              <f>'Daily Performance'!$G$2:$G$160</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$159</f>
+              <f>'Daily Performance'!$B$2:$B$160</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$159</f>
+              <f>'Daily Performance'!$I$2:$I$160</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M159"/>
+  <dimension ref="A1:M160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9312,6 +9312,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="160">
+      <c r="A160" s="27" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C160" s="28" t="n">
+        <v>68566.73</v>
+      </c>
+      <c r="D160" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E160" s="29" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F160" s="28" t="n">
+        <v>470293.49</v>
+      </c>
+      <c r="G160" s="28" t="n">
+        <v>470293.49</v>
+      </c>
+      <c r="H160" s="37" t="n">
+        <v>-29706.51</v>
+      </c>
+      <c r="I160" s="38" t="n">
+        <v>-0.0594</v>
+      </c>
+      <c r="J160" s="27" t="inlineStr">
+        <is>
+          <t>ซื้อ</t>
+        </is>
+      </c>
+      <c r="K160" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L160" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" s="27" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$160</f>
+              <f>'Daily Performance'!$B$2:$B$161</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$160</f>
+              <f>'Daily Performance'!$G$2:$G$161</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$160</f>
+              <f>'Daily Performance'!$B$2:$B$161</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$160</f>
+              <f>'Daily Performance'!$I$2:$I$161</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M160"/>
+  <dimension ref="A1:M161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9357,6 +9357,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="161">
+      <c r="A161" s="32" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="32" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C161" s="33" t="n">
+        <v>68100.53999999999</v>
+      </c>
+      <c r="D161" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" s="34" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F161" s="33" t="n">
+        <v>467095.92</v>
+      </c>
+      <c r="G161" s="33" t="n">
+        <v>467095.92</v>
+      </c>
+      <c r="H161" s="39" t="n">
+        <v>-32904.08</v>
+      </c>
+      <c r="I161" s="40" t="n">
+        <v>-0.0658</v>
+      </c>
+      <c r="J161" s="32" t="inlineStr">
+        <is>
+          <t>ขาย</t>
+        </is>
+      </c>
+      <c r="K161" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L161" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" s="32" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$161</f>
+              <f>'Daily Performance'!$B$2:$B$162</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$161</f>
+              <f>'Daily Performance'!$G$2:$G$162</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$161</f>
+              <f>'Daily Performance'!$B$2:$B$162</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$161</f>
+              <f>'Daily Performance'!$I$2:$I$162</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M161"/>
+  <dimension ref="A1:M162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9402,6 +9402,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" s="27" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C162" s="28" t="n">
+        <v>68027.03</v>
+      </c>
+      <c r="D162" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E162" s="29" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F162" s="28" t="n">
+        <v>466591.72</v>
+      </c>
+      <c r="G162" s="28" t="n">
+        <v>466591.72</v>
+      </c>
+      <c r="H162" s="37" t="n">
+        <v>-33408.28</v>
+      </c>
+      <c r="I162" s="38" t="n">
+        <v>-0.0668</v>
+      </c>
+      <c r="J162" s="27" t="inlineStr">
+        <is>
+          <t>ซื้อ</t>
+        </is>
+      </c>
+      <c r="K162" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L162" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" s="27" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$162</f>
+              <f>'Daily Performance'!$B$2:$B$163</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$162</f>
+              <f>'Daily Performance'!$G$2:$G$163</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$162</f>
+              <f>'Daily Performance'!$B$2:$B$163</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$162</f>
+              <f>'Daily Performance'!$I$2:$I$163</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M162"/>
+  <dimension ref="A1:M163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9447,6 +9447,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="163">
+      <c r="A163" s="32" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" s="32" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C163" s="33" t="n">
+        <v>68187.88</v>
+      </c>
+      <c r="D163" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" s="34" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F163" s="33" t="n">
+        <v>467694.98</v>
+      </c>
+      <c r="G163" s="33" t="n">
+        <v>467694.98</v>
+      </c>
+      <c r="H163" s="39" t="n">
+        <v>-32305.02</v>
+      </c>
+      <c r="I163" s="40" t="n">
+        <v>-0.0646</v>
+      </c>
+      <c r="J163" s="32" t="inlineStr">
+        <is>
+          <t>ซื้อ</t>
+        </is>
+      </c>
+      <c r="K163" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L163" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" s="32" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$163</f>
+              <f>'Daily Performance'!$B$2:$B$164</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$163</f>
+              <f>'Daily Performance'!$G$2:$G$164</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$163</f>
+              <f>'Daily Performance'!$B$2:$B$164</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$163</f>
+              <f>'Daily Performance'!$I$2:$I$164</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M163"/>
+  <dimension ref="A1:M164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9492,6 +9492,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="164">
+      <c r="A164" s="27" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C164" s="28" t="n">
+        <v>68198.92999999999</v>
+      </c>
+      <c r="D164" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E164" s="29" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F164" s="28" t="n">
+        <v>467770.77</v>
+      </c>
+      <c r="G164" s="28" t="n">
+        <v>467770.77</v>
+      </c>
+      <c r="H164" s="37" t="n">
+        <v>-32229.23</v>
+      </c>
+      <c r="I164" s="38" t="n">
+        <v>-0.0645</v>
+      </c>
+      <c r="J164" s="27" t="inlineStr">
+        <is>
+          <t>ซื้อ</t>
+        </is>
+      </c>
+      <c r="K164" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L164" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" s="27" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$164</f>
+              <f>'Daily Performance'!$B$2:$B$165</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$164</f>
+              <f>'Daily Performance'!$G$2:$G$165</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$164</f>
+              <f>'Daily Performance'!$B$2:$B$165</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$164</f>
+              <f>'Daily Performance'!$I$2:$I$165</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M164"/>
+  <dimension ref="A1:M165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9537,6 +9537,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="165">
+      <c r="A165" s="32" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" s="32" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C165" s="33" t="n">
+        <v>66439.72</v>
+      </c>
+      <c r="D165" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E165" s="34" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F165" s="33" t="n">
+        <v>455704.49</v>
+      </c>
+      <c r="G165" s="33" t="n">
+        <v>455704.49</v>
+      </c>
+      <c r="H165" s="39" t="n">
+        <v>-44295.51</v>
+      </c>
+      <c r="I165" s="40" t="n">
+        <v>-0.0886</v>
+      </c>
+      <c r="J165" s="32" t="inlineStr">
+        <is>
+          <t>ขาย</t>
+        </is>
+      </c>
+      <c r="K165" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L165" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" s="32" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$165</f>
+              <f>'Daily Performance'!$B$2:$B$166</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$165</f>
+              <f>'Daily Performance'!$G$2:$G$166</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$165</f>
+              <f>'Daily Performance'!$B$2:$B$166</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$165</f>
+              <f>'Daily Performance'!$I$2:$I$166</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M165"/>
+  <dimension ref="A1:M166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9582,6 +9582,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="166">
+      <c r="A166" s="27" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C166" s="28" t="n">
+        <v>66280.11</v>
+      </c>
+      <c r="D166" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" s="29" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F166" s="28" t="n">
+        <v>454609.72</v>
+      </c>
+      <c r="G166" s="28" t="n">
+        <v>454609.72</v>
+      </c>
+      <c r="H166" s="37" t="n">
+        <v>-45390.28</v>
+      </c>
+      <c r="I166" s="38" t="n">
+        <v>-0.09080000000000001</v>
+      </c>
+      <c r="J166" s="27" t="inlineStr">
+        <is>
+          <t>ถือ</t>
+        </is>
+      </c>
+      <c r="K166" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L166" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" s="27" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$166</f>
+              <f>'Daily Performance'!$B$2:$B$167</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$166</f>
+              <f>'Daily Performance'!$G$2:$G$167</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$166</f>
+              <f>'Daily Performance'!$B$2:$B$167</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$166</f>
+              <f>'Daily Performance'!$I$2:$I$167</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M166"/>
+  <dimension ref="A1:M167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9627,6 +9627,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="167">
+      <c r="A167" s="32" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" s="32" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C167" s="33" t="n">
+        <v>67010.14</v>
+      </c>
+      <c r="D167" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167" s="34" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F167" s="33" t="n">
+        <v>459616.98</v>
+      </c>
+      <c r="G167" s="33" t="n">
+        <v>459616.98</v>
+      </c>
+      <c r="H167" s="39" t="n">
+        <v>-40383.02</v>
+      </c>
+      <c r="I167" s="40" t="n">
+        <v>-0.0808</v>
+      </c>
+      <c r="J167" s="32" t="inlineStr">
+        <is>
+          <t>ซื้อ</t>
+        </is>
+      </c>
+      <c r="K167" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L167" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" s="32" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$167</f>
+              <f>'Daily Performance'!$B$2:$B$168</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$167</f>
+              <f>'Daily Performance'!$G$2:$G$168</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$167</f>
+              <f>'Daily Performance'!$B$2:$B$168</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$167</f>
+              <f>'Daily Performance'!$I$2:$I$168</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M167"/>
+  <dimension ref="A1:M168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9672,6 +9672,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="168">
+      <c r="A168" s="27" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C168" s="28" t="n">
+        <v>66831.8</v>
+      </c>
+      <c r="D168" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" s="29" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F168" s="28" t="n">
+        <v>458393.74</v>
+      </c>
+      <c r="G168" s="28" t="n">
+        <v>458393.74</v>
+      </c>
+      <c r="H168" s="37" t="n">
+        <v>-41606.26</v>
+      </c>
+      <c r="I168" s="38" t="n">
+        <v>-0.0832</v>
+      </c>
+      <c r="J168" s="27" t="inlineStr">
+        <is>
+          <t>ถือ</t>
+        </is>
+      </c>
+      <c r="K168" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L168" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M168" s="27" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$168</f>
+              <f>'Daily Performance'!$B$2:$B$169</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$168</f>
+              <f>'Daily Performance'!$G$2:$G$169</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$168</f>
+              <f>'Daily Performance'!$B$2:$B$169</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$168</f>
+              <f>'Daily Performance'!$I$2:$I$169</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M168"/>
+  <dimension ref="A1:M169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9717,6 +9717,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="169">
+      <c r="A169" s="32" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="32" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C169" s="33" t="n">
+        <v>66822.08</v>
+      </c>
+      <c r="D169" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" s="34" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F169" s="33" t="n">
+        <v>458327.05</v>
+      </c>
+      <c r="G169" s="33" t="n">
+        <v>458327.05</v>
+      </c>
+      <c r="H169" s="39" t="n">
+        <v>-41672.95</v>
+      </c>
+      <c r="I169" s="40" t="n">
+        <v>-0.0833</v>
+      </c>
+      <c r="J169" s="32" t="inlineStr">
+        <is>
+          <t>ขาย</t>
+        </is>
+      </c>
+      <c r="K169" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L169" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" s="32" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$169</f>
+              <f>'Daily Performance'!$B$2:$B$170</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$169</f>
+              <f>'Daily Performance'!$G$2:$G$170</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$169</f>
+              <f>'Daily Performance'!$B$2:$B$170</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$169</f>
+              <f>'Daily Performance'!$I$2:$I$170</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M169"/>
+  <dimension ref="A1:M170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9762,6 +9762,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="170">
+      <c r="A170" s="27" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C170" s="28" t="n">
+        <v>66161.49000000001</v>
+      </c>
+      <c r="D170" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E170" s="29" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F170" s="28" t="n">
+        <v>453796.1</v>
+      </c>
+      <c r="G170" s="28" t="n">
+        <v>453796.1</v>
+      </c>
+      <c r="H170" s="37" t="n">
+        <v>-46203.9</v>
+      </c>
+      <c r="I170" s="38" t="n">
+        <v>-0.0924</v>
+      </c>
+      <c r="J170" s="27" t="inlineStr">
+        <is>
+          <t>ขาย</t>
+        </is>
+      </c>
+      <c r="K170" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L170" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" s="27" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$170</f>
+              <f>'Daily Performance'!$B$2:$B$171</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$170</f>
+              <f>'Daily Performance'!$G$2:$G$171</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$170</f>
+              <f>'Daily Performance'!$B$2:$B$171</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$170</f>
+              <f>'Daily Performance'!$I$2:$I$171</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M170"/>
+  <dimension ref="A1:M171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9807,6 +9807,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="171">
+      <c r="A171" s="32" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="32" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C171" s="33" t="n">
+        <v>66006.07000000001</v>
+      </c>
+      <c r="D171" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E171" s="34" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F171" s="33" t="n">
+        <v>452730.13</v>
+      </c>
+      <c r="G171" s="33" t="n">
+        <v>452730.13</v>
+      </c>
+      <c r="H171" s="39" t="n">
+        <v>-47269.87</v>
+      </c>
+      <c r="I171" s="40" t="n">
+        <v>-0.09449999999999999</v>
+      </c>
+      <c r="J171" s="32" t="inlineStr">
+        <is>
+          <t>ขาย</t>
+        </is>
+      </c>
+      <c r="K171" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L171" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" s="32" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$171</f>
+              <f>'Daily Performance'!$B$2:$B$172</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$171</f>
+              <f>'Daily Performance'!$G$2:$G$172</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$171</f>
+              <f>'Daily Performance'!$B$2:$B$172</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$171</f>
+              <f>'Daily Performance'!$I$2:$I$172</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M171"/>
+  <dimension ref="A1:M172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9852,6 +9852,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="172">
+      <c r="A172" s="27" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C172" s="28" t="n">
+        <v>66655.2</v>
+      </c>
+      <c r="D172" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E172" s="29" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F172" s="28" t="n">
+        <v>457182.47</v>
+      </c>
+      <c r="G172" s="28" t="n">
+        <v>457182.47</v>
+      </c>
+      <c r="H172" s="37" t="n">
+        <v>-42817.53</v>
+      </c>
+      <c r="I172" s="38" t="n">
+        <v>-0.08560000000000001</v>
+      </c>
+      <c r="J172" s="27" t="inlineStr">
+        <is>
+          <t>ถือ</t>
+        </is>
+      </c>
+      <c r="K172" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L172" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M172" s="27" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$172</f>
+              <f>'Daily Performance'!$B$2:$B$173</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$172</f>
+              <f>'Daily Performance'!$G$2:$G$173</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$172</f>
+              <f>'Daily Performance'!$B$2:$B$173</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$172</f>
+              <f>'Daily Performance'!$I$2:$I$173</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M172"/>
+  <dimension ref="A1:M173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9897,6 +9897,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="173">
+      <c r="A173" s="32" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="32" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C173" s="33" t="n">
+        <v>66199.49000000001</v>
+      </c>
+      <c r="D173" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E173" s="34" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F173" s="33" t="n">
+        <v>454056.77</v>
+      </c>
+      <c r="G173" s="33" t="n">
+        <v>454056.77</v>
+      </c>
+      <c r="H173" s="39" t="n">
+        <v>-45943.23</v>
+      </c>
+      <c r="I173" s="40" t="n">
+        <v>-0.0919</v>
+      </c>
+      <c r="J173" s="32" t="inlineStr">
+        <is>
+          <t>ขาย</t>
+        </is>
+      </c>
+      <c r="K173" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L173" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M173" s="32" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$173</f>
+              <f>'Daily Performance'!$B$2:$B$174</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$173</f>
+              <f>'Daily Performance'!$G$2:$G$174</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$173</f>
+              <f>'Daily Performance'!$B$2:$B$174</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$173</f>
+              <f>'Daily Performance'!$I$2:$I$174</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M173"/>
+  <dimension ref="A1:M174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9942,6 +9942,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="174">
+      <c r="A174" s="27" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C174" s="28" t="n">
+        <v>66215.25</v>
+      </c>
+      <c r="D174" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E174" s="29" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F174" s="28" t="n">
+        <v>454164.9</v>
+      </c>
+      <c r="G174" s="28" t="n">
+        <v>454164.9</v>
+      </c>
+      <c r="H174" s="37" t="n">
+        <v>-45835.1</v>
+      </c>
+      <c r="I174" s="38" t="n">
+        <v>-0.0917</v>
+      </c>
+      <c r="J174" s="27" t="inlineStr">
+        <is>
+          <t>ขาย</t>
+        </is>
+      </c>
+      <c r="K174" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L174" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M174" s="27" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$174</f>
+              <f>'Daily Performance'!$B$2:$B$175</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$174</f>
+              <f>'Daily Performance'!$G$2:$G$175</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$174</f>
+              <f>'Daily Performance'!$B$2:$B$175</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$174</f>
+              <f>'Daily Performance'!$I$2:$I$175</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M174"/>
+  <dimension ref="A1:M175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9987,6 +9987,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="175">
+      <c r="A175" s="32" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" s="32" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C175" s="33" t="n">
+        <v>65925.66</v>
+      </c>
+      <c r="D175" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" s="34" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F175" s="33" t="n">
+        <v>452178.58</v>
+      </c>
+      <c r="G175" s="33" t="n">
+        <v>452178.58</v>
+      </c>
+      <c r="H175" s="39" t="n">
+        <v>-47821.42</v>
+      </c>
+      <c r="I175" s="40" t="n">
+        <v>-0.0956</v>
+      </c>
+      <c r="J175" s="32" t="inlineStr">
+        <is>
+          <t>ซื้อ</t>
+        </is>
+      </c>
+      <c r="K175" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L175" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M175" s="32" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$175</f>
+              <f>'Daily Performance'!$B$2:$B$176</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$175</f>
+              <f>'Daily Performance'!$G$2:$G$176</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$175</f>
+              <f>'Daily Performance'!$B$2:$B$176</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$175</f>
+              <f>'Daily Performance'!$I$2:$I$176</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M175"/>
+  <dimension ref="A1:M176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10032,6 +10032,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="176">
+      <c r="A176" s="27" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C176" s="28" t="n">
+        <v>66926.77</v>
+      </c>
+      <c r="D176" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E176" s="29" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F176" s="28" t="n">
+        <v>459045.15</v>
+      </c>
+      <c r="G176" s="28" t="n">
+        <v>459045.15</v>
+      </c>
+      <c r="H176" s="37" t="n">
+        <v>-40954.85</v>
+      </c>
+      <c r="I176" s="38" t="n">
+        <v>-0.0819</v>
+      </c>
+      <c r="J176" s="27" t="inlineStr">
+        <is>
+          <t>ซื้อ</t>
+        </is>
+      </c>
+      <c r="K176" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L176" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M176" s="27" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$176</f>
+              <f>'Daily Performance'!$B$2:$B$177</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$176</f>
+              <f>'Daily Performance'!$G$2:$G$177</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$176</f>
+              <f>'Daily Performance'!$B$2:$B$177</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$176</f>
+              <f>'Daily Performance'!$I$2:$I$177</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M176"/>
+  <dimension ref="A1:M177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10077,6 +10077,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="177">
+      <c r="A177" s="32" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" s="32" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C177" s="33" t="n">
+        <v>66782.64999999999</v>
+      </c>
+      <c r="D177" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E177" s="34" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F177" s="33" t="n">
+        <v>458056.61</v>
+      </c>
+      <c r="G177" s="33" t="n">
+        <v>458056.61</v>
+      </c>
+      <c r="H177" s="39" t="n">
+        <v>-41943.39</v>
+      </c>
+      <c r="I177" s="40" t="n">
+        <v>-0.0839</v>
+      </c>
+      <c r="J177" s="32" t="inlineStr">
+        <is>
+          <t>ถือ</t>
+        </is>
+      </c>
+      <c r="K177" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L177" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M177" s="32" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$177</f>
+              <f>'Daily Performance'!$B$2:$B$178</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$177</f>
+              <f>'Daily Performance'!$G$2:$G$178</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$177</f>
+              <f>'Daily Performance'!$B$2:$B$178</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$177</f>
+              <f>'Daily Performance'!$I$2:$I$178</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M177"/>
+  <dimension ref="A1:M178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10122,6 +10122,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="178">
+      <c r="A178" s="27" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="C178" s="28" t="n">
+        <v>66782.64999999999</v>
+      </c>
+      <c r="D178" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E178" s="29" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F178" s="28" t="n">
+        <v>458056.61</v>
+      </c>
+      <c r="G178" s="28" t="n">
+        <v>458056.61</v>
+      </c>
+      <c r="H178" s="37" t="n">
+        <v>-41943.39</v>
+      </c>
+      <c r="I178" s="38" t="n">
+        <v>-0.0839</v>
+      </c>
+      <c r="J178" s="27" t="inlineStr">
+        <is>
+          <t>ถือ</t>
+        </is>
+      </c>
+      <c r="K178" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L178" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M178" s="27" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$178</f>
+              <f>'Daily Performance'!$B$2:$B$179</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$178</f>
+              <f>'Daily Performance'!$G$2:$G$179</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$178</f>
+              <f>'Daily Performance'!$B$2:$B$179</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$178</f>
+              <f>'Daily Performance'!$I$2:$I$179</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M178"/>
+  <dimension ref="A1:M179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10167,6 +10167,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="179">
+      <c r="A179" s="32" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" s="32" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C179" s="33" t="n">
+        <v>66730.25</v>
+      </c>
+      <c r="D179" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E179" s="34" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F179" s="33" t="n">
+        <v>457697.23</v>
+      </c>
+      <c r="G179" s="33" t="n">
+        <v>457697.23</v>
+      </c>
+      <c r="H179" s="39" t="n">
+        <v>-42302.77</v>
+      </c>
+      <c r="I179" s="40" t="n">
+        <v>-0.08460000000000001</v>
+      </c>
+      <c r="J179" s="32" t="inlineStr">
+        <is>
+          <t>ถือ</t>
+        </is>
+      </c>
+      <c r="K179" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L179" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M179" s="32" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$179</f>
+              <f>'Daily Performance'!$B$2:$B$180</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$179</f>
+              <f>'Daily Performance'!$G$2:$G$180</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$179</f>
+              <f>'Daily Performance'!$B$2:$B$180</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$179</f>
+              <f>'Daily Performance'!$I$2:$I$180</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M179"/>
+  <dimension ref="A1:M180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10212,6 +10212,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="180">
+      <c r="A180" s="27" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C180" s="28" t="n">
+        <v>66809.85000000001</v>
+      </c>
+      <c r="D180" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E180" s="29" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F180" s="28" t="n">
+        <v>458243.17</v>
+      </c>
+      <c r="G180" s="28" t="n">
+        <v>458243.17</v>
+      </c>
+      <c r="H180" s="37" t="n">
+        <v>-41756.83</v>
+      </c>
+      <c r="I180" s="38" t="n">
+        <v>-0.08349999999999999</v>
+      </c>
+      <c r="J180" s="27" t="inlineStr">
+        <is>
+          <t>ซื้อ</t>
+        </is>
+      </c>
+      <c r="K180" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L180" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M180" s="27" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$180</f>
+              <f>'Daily Performance'!$B$2:$B$181</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$180</f>
+              <f>'Daily Performance'!$G$2:$G$181</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$180</f>
+              <f>'Daily Performance'!$B$2:$B$181</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$180</f>
+              <f>'Daily Performance'!$I$2:$I$181</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M180"/>
+  <dimension ref="A1:M181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10257,6 +10257,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="181">
+      <c r="A181" s="32" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" s="32" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C181" s="33" t="n">
+        <v>66222.47</v>
+      </c>
+      <c r="D181" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" s="34" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F181" s="33" t="n">
+        <v>454214.37</v>
+      </c>
+      <c r="G181" s="33" t="n">
+        <v>454214.37</v>
+      </c>
+      <c r="H181" s="39" t="n">
+        <v>-45785.63</v>
+      </c>
+      <c r="I181" s="40" t="n">
+        <v>-0.0916</v>
+      </c>
+      <c r="J181" s="32" t="inlineStr">
+        <is>
+          <t>ขาย</t>
+        </is>
+      </c>
+      <c r="K181" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L181" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" s="32" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$181</f>
+              <f>'Daily Performance'!$B$2:$B$182</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$181</f>
+              <f>'Daily Performance'!$G$2:$G$182</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$181</f>
+              <f>'Daily Performance'!$B$2:$B$182</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$181</f>
+              <f>'Daily Performance'!$I$2:$I$182</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M181"/>
+  <dimension ref="A1:M182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10302,6 +10302,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="182">
+      <c r="A182" s="27" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C182" s="28" t="n">
+        <v>65885.56</v>
+      </c>
+      <c r="D182" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E182" s="29" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F182" s="28" t="n">
+        <v>451903.53</v>
+      </c>
+      <c r="G182" s="28" t="n">
+        <v>451903.53</v>
+      </c>
+      <c r="H182" s="37" t="n">
+        <v>-48096.47</v>
+      </c>
+      <c r="I182" s="38" t="n">
+        <v>-0.09619999999999999</v>
+      </c>
+      <c r="J182" s="27" t="inlineStr">
+        <is>
+          <t>ซื้อ</t>
+        </is>
+      </c>
+      <c r="K182" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L182" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M182" s="27" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$182</f>
+              <f>'Daily Performance'!$B$2:$B$183</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$182</f>
+              <f>'Daily Performance'!$G$2:$G$183</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$182</f>
+              <f>'Daily Performance'!$B$2:$B$183</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$182</f>
+              <f>'Daily Performance'!$I$2:$I$183</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M182"/>
+  <dimension ref="A1:M183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10347,6 +10347,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="183">
+      <c r="A183" s="32" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" s="32" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C183" s="33" t="n">
+        <v>66324.64999999999</v>
+      </c>
+      <c r="D183" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E183" s="34" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F183" s="33" t="n">
+        <v>454915.24</v>
+      </c>
+      <c r="G183" s="33" t="n">
+        <v>454915.24</v>
+      </c>
+      <c r="H183" s="39" t="n">
+        <v>-45084.76</v>
+      </c>
+      <c r="I183" s="40" t="n">
+        <v>-0.0902</v>
+      </c>
+      <c r="J183" s="32" t="inlineStr">
+        <is>
+          <t>ซื้อ</t>
+        </is>
+      </c>
+      <c r="K183" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L183" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M183" s="32" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$183</f>
+              <f>'Daily Performance'!$B$2:$B$184</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$183</f>
+              <f>'Daily Performance'!$G$2:$G$184</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$183</f>
+              <f>'Daily Performance'!$B$2:$B$184</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$183</f>
+              <f>'Daily Performance'!$I$2:$I$184</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M183"/>
+  <dimension ref="A1:M184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10392,6 +10392,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="184">
+      <c r="A184" s="27" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="C184" s="28" t="n">
+        <v>66175.2</v>
+      </c>
+      <c r="D184" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E184" s="29" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F184" s="28" t="n">
+        <v>453890.18</v>
+      </c>
+      <c r="G184" s="28" t="n">
+        <v>453890.18</v>
+      </c>
+      <c r="H184" s="37" t="n">
+        <v>-46109.82</v>
+      </c>
+      <c r="I184" s="38" t="n">
+        <v>-0.0922</v>
+      </c>
+      <c r="J184" s="27" t="inlineStr">
+        <is>
+          <t>ขาย</t>
+        </is>
+      </c>
+      <c r="K184" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L184" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M184" s="27" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$184</f>
+              <f>'Daily Performance'!$B$2:$B$185</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$184</f>
+              <f>'Daily Performance'!$G$2:$G$185</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$184</f>
+              <f>'Daily Performance'!$B$2:$B$185</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$184</f>
+              <f>'Daily Performance'!$I$2:$I$185</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M184"/>
+  <dimension ref="A1:M185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10437,6 +10437,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="185">
+      <c r="A185" s="32" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" s="32" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="C185" s="33" t="n">
+        <v>66086.69</v>
+      </c>
+      <c r="D185" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E185" s="34" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F185" s="33" t="n">
+        <v>453283.06</v>
+      </c>
+      <c r="G185" s="33" t="n">
+        <v>453283.06</v>
+      </c>
+      <c r="H185" s="39" t="n">
+        <v>-46716.94</v>
+      </c>
+      <c r="I185" s="40" t="n">
+        <v>-0.0934</v>
+      </c>
+      <c r="J185" s="32" t="inlineStr">
+        <is>
+          <t>ขาย</t>
+        </is>
+      </c>
+      <c r="K185" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L185" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M185" s="32" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$185</f>
+              <f>'Daily Performance'!$B$2:$B$186</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$185</f>
+              <f>'Daily Performance'!$G$2:$G$186</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$185</f>
+              <f>'Daily Performance'!$B$2:$B$186</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$185</f>
+              <f>'Daily Performance'!$I$2:$I$186</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M185"/>
+  <dimension ref="A1:M186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10482,6 +10482,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="186">
+      <c r="A186" s="27" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C186" s="28" t="n">
+        <v>66664.92</v>
+      </c>
+      <c r="D186" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E186" s="29" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F186" s="28" t="n">
+        <v>457249.1</v>
+      </c>
+      <c r="G186" s="28" t="n">
+        <v>457249.1</v>
+      </c>
+      <c r="H186" s="37" t="n">
+        <v>-42750.9</v>
+      </c>
+      <c r="I186" s="38" t="n">
+        <v>-0.08550000000000001</v>
+      </c>
+      <c r="J186" s="27" t="inlineStr">
+        <is>
+          <t>ซื้อ</t>
+        </is>
+      </c>
+      <c r="K186" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L186" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M186" s="27" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$186</f>
+              <f>'Daily Performance'!$B$2:$B$187</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$186</f>
+              <f>'Daily Performance'!$G$2:$G$187</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$186</f>
+              <f>'Daily Performance'!$B$2:$B$187</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$186</f>
+              <f>'Daily Performance'!$I$2:$I$187</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M186"/>
+  <dimension ref="A1:M187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10527,6 +10527,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="187">
+      <c r="A187" s="32" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" s="32" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C187" s="33" t="n">
+        <v>65858.21000000001</v>
+      </c>
+      <c r="D187" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E187" s="34" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F187" s="33" t="n">
+        <v>451715.96</v>
+      </c>
+      <c r="G187" s="33" t="n">
+        <v>451715.96</v>
+      </c>
+      <c r="H187" s="39" t="n">
+        <v>-48284.04</v>
+      </c>
+      <c r="I187" s="40" t="n">
+        <v>-0.09660000000000001</v>
+      </c>
+      <c r="J187" s="32" t="inlineStr">
+        <is>
+          <t>ขาย</t>
+        </is>
+      </c>
+      <c r="K187" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L187" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M187" s="32" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$187</f>
+              <f>'Daily Performance'!$B$2:$B$188</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$187</f>
+              <f>'Daily Performance'!$G$2:$G$188</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$187</f>
+              <f>'Daily Performance'!$B$2:$B$188</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$187</f>
+              <f>'Daily Performance'!$I$2:$I$188</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M187"/>
+  <dimension ref="A1:M188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10572,6 +10572,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="188">
+      <c r="A188" s="27" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C188" s="28" t="n">
+        <v>65746.89999999999</v>
+      </c>
+      <c r="D188" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E188" s="29" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F188" s="28" t="n">
+        <v>450952.53</v>
+      </c>
+      <c r="G188" s="28" t="n">
+        <v>450952.53</v>
+      </c>
+      <c r="H188" s="37" t="n">
+        <v>-49047.47</v>
+      </c>
+      <c r="I188" s="38" t="n">
+        <v>-0.09810000000000001</v>
+      </c>
+      <c r="J188" s="27" t="inlineStr">
+        <is>
+          <t>ถือ</t>
+        </is>
+      </c>
+      <c r="K188" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L188" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M188" s="27" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$188</f>
+              <f>'Daily Performance'!$B$2:$B$189</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$188</f>
+              <f>'Daily Performance'!$G$2:$G$189</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$188</f>
+              <f>'Daily Performance'!$B$2:$B$189</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$188</f>
+              <f>'Daily Performance'!$I$2:$I$189</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M188"/>
+  <dimension ref="A1:M189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10617,6 +10617,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="189">
+      <c r="A189" s="32" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" s="32" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C189" s="33" t="n">
+        <v>65354.26</v>
+      </c>
+      <c r="D189" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E189" s="34" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F189" s="33" t="n">
+        <v>448259.41</v>
+      </c>
+      <c r="G189" s="33" t="n">
+        <v>448259.41</v>
+      </c>
+      <c r="H189" s="39" t="n">
+        <v>-51740.59</v>
+      </c>
+      <c r="I189" s="40" t="n">
+        <v>-0.1035</v>
+      </c>
+      <c r="J189" s="32" t="inlineStr">
+        <is>
+          <t>ขาย</t>
+        </is>
+      </c>
+      <c r="K189" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L189" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M189" s="32" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$189</f>
+              <f>'Daily Performance'!$B$2:$B$190</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$189</f>
+              <f>'Daily Performance'!$G$2:$G$190</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$189</f>
+              <f>'Daily Performance'!$B$2:$B$190</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$189</f>
+              <f>'Daily Performance'!$I$2:$I$190</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M189"/>
+  <dimension ref="A1:M190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10662,6 +10662,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="190">
+      <c r="A190" s="27" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C190" s="28" t="n">
+        <v>64217.65</v>
+      </c>
+      <c r="D190" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E190" s="29" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F190" s="28" t="n">
+        <v>440463.49</v>
+      </c>
+      <c r="G190" s="28" t="n">
+        <v>440463.49</v>
+      </c>
+      <c r="H190" s="37" t="n">
+        <v>-59536.51</v>
+      </c>
+      <c r="I190" s="38" t="n">
+        <v>-0.1191</v>
+      </c>
+      <c r="J190" s="27" t="inlineStr">
+        <is>
+          <t>ถือ</t>
+        </is>
+      </c>
+      <c r="K190" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L190" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M190" s="27" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$190</f>
+              <f>'Daily Performance'!$B$2:$B$191</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$190</f>
+              <f>'Daily Performance'!$G$2:$G$191</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$190</f>
+              <f>'Daily Performance'!$B$2:$B$191</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$190</f>
+              <f>'Daily Performance'!$I$2:$I$191</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M190"/>
+  <dimension ref="A1:M191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10707,6 +10707,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="191">
+      <c r="A191" s="32" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" s="32" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C191" s="33" t="n">
+        <v>63955.66</v>
+      </c>
+      <c r="D191" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E191" s="34" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F191" s="33" t="n">
+        <v>438666.5</v>
+      </c>
+      <c r="G191" s="33" t="n">
+        <v>438666.5</v>
+      </c>
+      <c r="H191" s="39" t="n">
+        <v>-61333.5</v>
+      </c>
+      <c r="I191" s="40" t="n">
+        <v>-0.1227</v>
+      </c>
+      <c r="J191" s="32" t="inlineStr">
+        <is>
+          <t>ซื้อ</t>
+        </is>
+      </c>
+      <c r="K191" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L191" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M191" s="32" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$191</f>
+              <f>'Daily Performance'!$B$2:$B$192</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$191</f>
+              <f>'Daily Performance'!$G$2:$G$192</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$191</f>
+              <f>'Daily Performance'!$B$2:$B$192</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$191</f>
+              <f>'Daily Performance'!$I$2:$I$192</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M191"/>
+  <dimension ref="A1:M192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10752,6 +10752,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="192">
+      <c r="A192" s="27" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="C192" s="28" t="n">
+        <v>63955.66</v>
+      </c>
+      <c r="D192" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E192" s="29" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F192" s="28" t="n">
+        <v>438666.5</v>
+      </c>
+      <c r="G192" s="28" t="n">
+        <v>438666.5</v>
+      </c>
+      <c r="H192" s="37" t="n">
+        <v>-61333.5</v>
+      </c>
+      <c r="I192" s="38" t="n">
+        <v>-0.1227</v>
+      </c>
+      <c r="J192" s="27" t="inlineStr">
+        <is>
+          <t>ซื้อ</t>
+        </is>
+      </c>
+      <c r="K192" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L192" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M192" s="27" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$192</f>
+              <f>'Daily Performance'!$B$2:$B$193</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$192</f>
+              <f>'Daily Performance'!$G$2:$G$193</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$192</f>
+              <f>'Daily Performance'!$B$2:$B$193</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$192</f>
+              <f>'Daily Performance'!$I$2:$I$193</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M192"/>
+  <dimension ref="A1:M193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10797,6 +10797,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="193">
+      <c r="A193" s="32" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" s="32" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C193" s="33" t="n">
+        <v>64256.59</v>
+      </c>
+      <c r="D193" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E193" s="34" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F193" s="33" t="n">
+        <v>440730.58</v>
+      </c>
+      <c r="G193" s="33" t="n">
+        <v>440730.58</v>
+      </c>
+      <c r="H193" s="39" t="n">
+        <v>-59269.42</v>
+      </c>
+      <c r="I193" s="40" t="n">
+        <v>-0.1185</v>
+      </c>
+      <c r="J193" s="32" t="inlineStr">
+        <is>
+          <t>ถือ</t>
+        </is>
+      </c>
+      <c r="K193" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L193" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M193" s="32" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$193</f>
+              <f>'Daily Performance'!$B$2:$B$194</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$193</f>
+              <f>'Daily Performance'!$G$2:$G$194</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$193</f>
+              <f>'Daily Performance'!$B$2:$B$194</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$193</f>
+              <f>'Daily Performance'!$I$2:$I$194</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M193"/>
+  <dimension ref="A1:M194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10842,6 +10842,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" s="27" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C194" s="28" t="n">
+        <v>64049.63</v>
+      </c>
+      <c r="D194" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E194" s="29" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F194" s="28" t="n">
+        <v>439311.08</v>
+      </c>
+      <c r="G194" s="28" t="n">
+        <v>439311.08</v>
+      </c>
+      <c r="H194" s="37" t="n">
+        <v>-60688.92</v>
+      </c>
+      <c r="I194" s="38" t="n">
+        <v>-0.1214</v>
+      </c>
+      <c r="J194" s="27" t="inlineStr">
+        <is>
+          <t>ขาย</t>
+        </is>
+      </c>
+      <c r="K194" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L194" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M194" s="27" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$194</f>
+              <f>'Daily Performance'!$B$2:$B$195</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$194</f>
+              <f>'Daily Performance'!$G$2:$G$195</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$194</f>
+              <f>'Daily Performance'!$B$2:$B$195</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$194</f>
+              <f>'Daily Performance'!$I$2:$I$195</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M194"/>
+  <dimension ref="A1:M195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10887,6 +10887,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="195">
+      <c r="A195" s="32" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" s="32" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C195" s="33" t="n">
+        <v>64740.82</v>
+      </c>
+      <c r="D195" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E195" s="34" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F195" s="33" t="n">
+        <v>444051.9</v>
+      </c>
+      <c r="G195" s="33" t="n">
+        <v>444051.9</v>
+      </c>
+      <c r="H195" s="39" t="n">
+        <v>-55948.1</v>
+      </c>
+      <c r="I195" s="40" t="n">
+        <v>-0.1119</v>
+      </c>
+      <c r="J195" s="32" t="inlineStr">
+        <is>
+          <t>ถือ</t>
+        </is>
+      </c>
+      <c r="K195" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L195" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M195" s="32" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$195</f>
+              <f>'Daily Performance'!$B$2:$B$196</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$195</f>
+              <f>'Daily Performance'!$G$2:$G$196</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$195</f>
+              <f>'Daily Performance'!$B$2:$B$196</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$195</f>
+              <f>'Daily Performance'!$I$2:$I$196</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M195"/>
+  <dimension ref="A1:M196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10932,6 +10932,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="196">
+      <c r="A196" s="27" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C196" s="28" t="n">
+        <v>64439.21</v>
+      </c>
+      <c r="D196" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E196" s="29" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F196" s="28" t="n">
+        <v>441983.13</v>
+      </c>
+      <c r="G196" s="28" t="n">
+        <v>441983.13</v>
+      </c>
+      <c r="H196" s="37" t="n">
+        <v>-58016.87</v>
+      </c>
+      <c r="I196" s="38" t="n">
+        <v>-0.116</v>
+      </c>
+      <c r="J196" s="27" t="inlineStr">
+        <is>
+          <t>ขาย</t>
+        </is>
+      </c>
+      <c r="K196" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L196" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M196" s="27" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$196</f>
+              <f>'Daily Performance'!$B$2:$B$197</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$196</f>
+              <f>'Daily Performance'!$G$2:$G$197</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$196</f>
+              <f>'Daily Performance'!$B$2:$B$197</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$196</f>
+              <f>'Daily Performance'!$I$2:$I$197</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M196"/>
+  <dimension ref="A1:M197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10977,6 +10977,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="197">
+      <c r="A197" s="32" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" s="32" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C197" s="33" t="n">
+        <v>63618.19</v>
+      </c>
+      <c r="D197" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E197" s="34" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F197" s="33" t="n">
+        <v>436351.83</v>
+      </c>
+      <c r="G197" s="33" t="n">
+        <v>436351.83</v>
+      </c>
+      <c r="H197" s="39" t="n">
+        <v>-63648.17</v>
+      </c>
+      <c r="I197" s="40" t="n">
+        <v>-0.1273</v>
+      </c>
+      <c r="J197" s="32" t="inlineStr">
+        <is>
+          <t>ขาย</t>
+        </is>
+      </c>
+      <c r="K197" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L197" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M197" s="32" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Gold_Forward_Test_Report.xlsx
+++ b/Gold_Forward_Test_Report.xlsx
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$197</f>
+              <f>'Daily Performance'!$B$2:$B$198</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$G$2:$G$197</f>
+              <f>'Daily Performance'!$G$2:$G$198</f>
             </numRef>
           </val>
         </ser>
@@ -607,12 +607,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Performance'!$B$2:$B$197</f>
+              <f>'Daily Performance'!$B$2:$B$198</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Performance'!$I$2:$I$197</f>
+              <f>'Daily Performance'!$I$2:$I$198</f>
             </numRef>
           </val>
         </ser>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M197"/>
+  <dimension ref="A1:M198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -11022,6 +11022,51 @@
         <v>15</v>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" s="27" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="C198" s="28" t="n">
+        <v>62216.3</v>
+      </c>
+      <c r="D198" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E198" s="29" t="n">
+        <v>6.858916</v>
+      </c>
+      <c r="F198" s="28" t="n">
+        <v>426736.4</v>
+      </c>
+      <c r="G198" s="28" t="n">
+        <v>426736.4</v>
+      </c>
+      <c r="H198" s="37" t="n">
+        <v>-73263.60000000001</v>
+      </c>
+      <c r="I198" s="38" t="n">
+        <v>-0.1465</v>
+      </c>
+      <c r="J198" s="27" t="inlineStr">
+        <is>
+          <t>ขาย</t>
+        </is>
+      </c>
+      <c r="K198" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L198" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M198" s="27" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
